--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237278</v>
+        <v>120237289</v>
       </c>
       <c r="B2" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447033</v>
+        <v>447108</v>
       </c>
       <c r="R2" t="n">
-        <v>6810319</v>
+        <v>6810318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237292</v>
+        <v>120237300</v>
       </c>
       <c r="B3" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447141</v>
+        <v>447112</v>
       </c>
       <c r="R3" t="n">
-        <v>6810377</v>
+        <v>6810364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237277</v>
+        <v>120237276</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447039</v>
+        <v>447061</v>
       </c>
       <c r="R4" t="n">
-        <v>6810326</v>
+        <v>6810331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237293</v>
+        <v>120237277</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447133</v>
+        <v>447039</v>
       </c>
       <c r="R5" t="n">
-        <v>6810336</v>
+        <v>6810326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
         <v>120237295</v>
       </c>
       <c r="B6" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237294</v>
+        <v>120237301</v>
       </c>
       <c r="B7" t="n">
-        <v>78560</v>
+        <v>77479</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447133</v>
+        <v>447132</v>
       </c>
       <c r="R7" t="n">
-        <v>6810330</v>
+        <v>6810359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237290</v>
+        <v>120237294</v>
       </c>
       <c r="B8" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447116</v>
+        <v>447133</v>
       </c>
       <c r="R8" t="n">
-        <v>6810359</v>
+        <v>6810330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237299</v>
+        <v>120237290</v>
       </c>
       <c r="B9" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447102</v>
+        <v>447116</v>
       </c>
       <c r="R9" t="n">
-        <v>6810347</v>
+        <v>6810359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120237289</v>
+        <v>120237299</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447108</v>
+        <v>447102</v>
       </c>
       <c r="R10" t="n">
-        <v>6810318</v>
+        <v>6810347</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120237298</v>
+        <v>120237278</v>
       </c>
       <c r="B11" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447110</v>
+        <v>447033</v>
       </c>
       <c r="R11" t="n">
-        <v>6810336</v>
+        <v>6810319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237300</v>
+        <v>120237298</v>
       </c>
       <c r="B12" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447112</v>
+        <v>447110</v>
       </c>
       <c r="R12" t="n">
-        <v>6810364</v>
+        <v>6810336</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237297</v>
+        <v>120237292</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447117</v>
+        <v>447141</v>
       </c>
       <c r="R13" t="n">
-        <v>6810334</v>
+        <v>6810377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120237301</v>
+        <v>120237302</v>
       </c>
       <c r="B14" t="n">
-        <v>77463</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
         <v>447132</v>
       </c>
       <c r="R14" t="n">
-        <v>6810359</v>
+        <v>6810361</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120237303</v>
+        <v>120237293</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447119</v>
+        <v>447133</v>
       </c>
       <c r="R15" t="n">
-        <v>6810321</v>
+        <v>6810336</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237291</v>
+        <v>120237297</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447116</v>
+        <v>447117</v>
       </c>
       <c r="R16" t="n">
-        <v>6810359</v>
+        <v>6810334</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237302</v>
+        <v>120237303</v>
       </c>
       <c r="B17" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2446,21 +2446,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447132</v>
+        <v>447119</v>
       </c>
       <c r="R17" t="n">
-        <v>6810361</v>
+        <v>6810321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237276</v>
+        <v>120237291</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447061</v>
+        <v>447116</v>
       </c>
       <c r="R18" t="n">
-        <v>6810331</v>
+        <v>6810359</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237289</v>
+        <v>120237290</v>
       </c>
       <c r="B2" t="n">
         <v>78576</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447108</v>
+        <v>447116</v>
       </c>
       <c r="R2" t="n">
-        <v>6810318</v>
+        <v>6810359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237300</v>
+        <v>120237292</v>
       </c>
       <c r="B3" t="n">
         <v>78576</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447112</v>
+        <v>447141</v>
       </c>
       <c r="R3" t="n">
-        <v>6810364</v>
+        <v>6810377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237276</v>
+        <v>120237289</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447061</v>
+        <v>447108</v>
       </c>
       <c r="R4" t="n">
-        <v>6810331</v>
+        <v>6810318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237277</v>
+        <v>120237295</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447039</v>
+        <v>447114</v>
       </c>
       <c r="R5" t="n">
-        <v>6810326</v>
+        <v>6810324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237295</v>
+        <v>120237302</v>
       </c>
       <c r="B6" t="n">
-        <v>78576</v>
+        <v>74654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447114</v>
+        <v>447132</v>
       </c>
       <c r="R6" t="n">
-        <v>6810324</v>
+        <v>6810361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237294</v>
+        <v>120237298</v>
       </c>
       <c r="B8" t="n">
         <v>78576</v>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447133</v>
+        <v>447110</v>
       </c>
       <c r="R8" t="n">
-        <v>6810330</v>
+        <v>6810336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237290</v>
+        <v>120237277</v>
       </c>
       <c r="B9" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447116</v>
+        <v>447039</v>
       </c>
       <c r="R9" t="n">
-        <v>6810359</v>
+        <v>6810326</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120237299</v>
+        <v>120237276</v>
       </c>
       <c r="B10" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447102</v>
+        <v>447061</v>
       </c>
       <c r="R10" t="n">
-        <v>6810347</v>
+        <v>6810331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237298</v>
+        <v>120237303</v>
       </c>
       <c r="B12" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447110</v>
+        <v>447119</v>
       </c>
       <c r="R12" t="n">
-        <v>6810336</v>
+        <v>6810321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237292</v>
+        <v>120237294</v>
       </c>
       <c r="B13" t="n">
         <v>78576</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447141</v>
+        <v>447133</v>
       </c>
       <c r="R13" t="n">
-        <v>6810377</v>
+        <v>6810330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120237302</v>
+        <v>120237299</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>78576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447132</v>
+        <v>447102</v>
       </c>
       <c r="R14" t="n">
-        <v>6810361</v>
+        <v>6810347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120237293</v>
+        <v>120237297</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447133</v>
+        <v>447117</v>
       </c>
       <c r="R15" t="n">
-        <v>6810336</v>
+        <v>6810334</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237297</v>
+        <v>120237291</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447117</v>
+        <v>447116</v>
       </c>
       <c r="R16" t="n">
-        <v>6810334</v>
+        <v>6810359</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237303</v>
+        <v>120237293</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447119</v>
+        <v>447133</v>
       </c>
       <c r="R17" t="n">
-        <v>6810321</v>
+        <v>6810336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237291</v>
+        <v>120237300</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447116</v>
+        <v>447112</v>
       </c>
       <c r="R18" t="n">
-        <v>6810359</v>
+        <v>6810364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237290</v>
+        <v>120237299</v>
       </c>
       <c r="B2" t="n">
         <v>78576</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447116</v>
+        <v>447102</v>
       </c>
       <c r="R2" t="n">
-        <v>6810359</v>
+        <v>6810347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237292</v>
+        <v>120237277</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447141</v>
+        <v>447039</v>
       </c>
       <c r="R3" t="n">
-        <v>6810377</v>
+        <v>6810326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237289</v>
+        <v>120237290</v>
       </c>
       <c r="B4" t="n">
         <v>78576</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447108</v>
+        <v>447116</v>
       </c>
       <c r="R4" t="n">
-        <v>6810318</v>
+        <v>6810359</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237295</v>
+        <v>120237300</v>
       </c>
       <c r="B5" t="n">
         <v>78576</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447114</v>
+        <v>447112</v>
       </c>
       <c r="R5" t="n">
-        <v>6810324</v>
+        <v>6810364</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237302</v>
+        <v>120237295</v>
       </c>
       <c r="B6" t="n">
-        <v>74654</v>
+        <v>78576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447132</v>
+        <v>447114</v>
       </c>
       <c r="R6" t="n">
-        <v>6810361</v>
+        <v>6810324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237301</v>
+        <v>120237297</v>
       </c>
       <c r="B7" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447132</v>
+        <v>447117</v>
       </c>
       <c r="R7" t="n">
-        <v>6810359</v>
+        <v>6810334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237298</v>
+        <v>120237291</v>
       </c>
       <c r="B8" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447110</v>
+        <v>447116</v>
       </c>
       <c r="R8" t="n">
-        <v>6810336</v>
+        <v>6810359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237277</v>
+        <v>120237294</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447039</v>
+        <v>447133</v>
       </c>
       <c r="R9" t="n">
-        <v>6810326</v>
+        <v>6810330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120237276</v>
+        <v>120237302</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447061</v>
+        <v>447132</v>
       </c>
       <c r="R10" t="n">
-        <v>6810331</v>
+        <v>6810361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120237278</v>
+        <v>120237276</v>
       </c>
       <c r="B11" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447033</v>
+        <v>447061</v>
       </c>
       <c r="R11" t="n">
-        <v>6810319</v>
+        <v>6810331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237303</v>
+        <v>120237298</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447119</v>
+        <v>447110</v>
       </c>
       <c r="R12" t="n">
-        <v>6810321</v>
+        <v>6810336</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237294</v>
+        <v>120237303</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447133</v>
+        <v>447119</v>
       </c>
       <c r="R13" t="n">
-        <v>6810330</v>
+        <v>6810321</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120237299</v>
+        <v>120237293</v>
       </c>
       <c r="B14" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447102</v>
+        <v>447133</v>
       </c>
       <c r="R14" t="n">
-        <v>6810347</v>
+        <v>6810336</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120237297</v>
+        <v>120237289</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447117</v>
+        <v>447108</v>
       </c>
       <c r="R15" t="n">
-        <v>6810334</v>
+        <v>6810318</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237291</v>
+        <v>120237292</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447116</v>
+        <v>447141</v>
       </c>
       <c r="R16" t="n">
-        <v>6810359</v>
+        <v>6810377</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237293</v>
+        <v>120237278</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2446,21 +2446,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447133</v>
+        <v>447033</v>
       </c>
       <c r="R17" t="n">
-        <v>6810336</v>
+        <v>6810319</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237300</v>
+        <v>120237301</v>
       </c>
       <c r="B18" t="n">
-        <v>78576</v>
+        <v>77479</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447112</v>
+        <v>447132</v>
       </c>
       <c r="R18" t="n">
-        <v>6810364</v>
+        <v>6810359</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237300</v>
+        <v>120237295</v>
       </c>
       <c r="B5" t="n">
         <v>78576</v>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447112</v>
+        <v>447114</v>
       </c>
       <c r="R5" t="n">
-        <v>6810364</v>
+        <v>6810324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237295</v>
+        <v>120237300</v>
       </c>
       <c r="B6" t="n">
         <v>78576</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447114</v>
+        <v>447112</v>
       </c>
       <c r="R6" t="n">
-        <v>6810324</v>
+        <v>6810364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237299</v>
+        <v>120237303</v>
       </c>
       <c r="B2" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447102</v>
+        <v>447119</v>
       </c>
       <c r="R2" t="n">
-        <v>6810347</v>
+        <v>6810321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237277</v>
+        <v>120237297</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447039</v>
+        <v>447117</v>
       </c>
       <c r="R3" t="n">
-        <v>6810326</v>
+        <v>6810334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237290</v>
+        <v>120237295</v>
       </c>
       <c r="B4" t="n">
         <v>78576</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447116</v>
+        <v>447114</v>
       </c>
       <c r="R4" t="n">
-        <v>6810359</v>
+        <v>6810324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237295</v>
+        <v>120237301</v>
       </c>
       <c r="B5" t="n">
-        <v>78576</v>
+        <v>77479</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447114</v>
+        <v>447132</v>
       </c>
       <c r="R5" t="n">
-        <v>6810324</v>
+        <v>6810359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237300</v>
+        <v>120237278</v>
       </c>
       <c r="B6" t="n">
         <v>78576</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447112</v>
+        <v>447033</v>
       </c>
       <c r="R6" t="n">
-        <v>6810364</v>
+        <v>6810319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237297</v>
+        <v>120237293</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447117</v>
+        <v>447133</v>
       </c>
       <c r="R7" t="n">
-        <v>6810334</v>
+        <v>6810336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237291</v>
+        <v>120237292</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447116</v>
+        <v>447141</v>
       </c>
       <c r="R8" t="n">
-        <v>6810359</v>
+        <v>6810377</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237294</v>
+        <v>120237277</v>
       </c>
       <c r="B9" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447133</v>
+        <v>447039</v>
       </c>
       <c r="R9" t="n">
-        <v>6810330</v>
+        <v>6810326</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120237276</v>
+        <v>120237299</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447061</v>
+        <v>447102</v>
       </c>
       <c r="R11" t="n">
-        <v>6810331</v>
+        <v>6810347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237298</v>
+        <v>120237291</v>
       </c>
       <c r="B12" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447110</v>
+        <v>447116</v>
       </c>
       <c r="R12" t="n">
-        <v>6810336</v>
+        <v>6810359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237303</v>
+        <v>120237294</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447119</v>
+        <v>447133</v>
       </c>
       <c r="R13" t="n">
-        <v>6810321</v>
+        <v>6810330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120237293</v>
+        <v>120237298</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,21 +2095,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447133</v>
+        <v>447110</v>
       </c>
       <c r="R14" t="n">
         <v>6810336</v>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120237289</v>
+        <v>120237300</v>
       </c>
       <c r="B15" t="n">
         <v>78576</v>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447108</v>
+        <v>447112</v>
       </c>
       <c r="R15" t="n">
-        <v>6810318</v>
+        <v>6810364</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237292</v>
+        <v>120237276</v>
       </c>
       <c r="B16" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447141</v>
+        <v>447061</v>
       </c>
       <c r="R16" t="n">
-        <v>6810377</v>
+        <v>6810331</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237278</v>
+        <v>120237290</v>
       </c>
       <c r="B17" t="n">
         <v>78576</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447033</v>
+        <v>447116</v>
       </c>
       <c r="R17" t="n">
-        <v>6810319</v>
+        <v>6810359</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237301</v>
+        <v>120237289</v>
       </c>
       <c r="B18" t="n">
-        <v>77479</v>
+        <v>78576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447132</v>
+        <v>447108</v>
       </c>
       <c r="R18" t="n">
-        <v>6810359</v>
+        <v>6810318</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237303</v>
+        <v>120237301</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447119</v>
+        <v>447132</v>
       </c>
       <c r="R2" t="n">
-        <v>6810321</v>
+        <v>6810359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237297</v>
+        <v>120237290</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447117</v>
+        <v>447116</v>
       </c>
       <c r="R3" t="n">
-        <v>6810334</v>
+        <v>6810359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237295</v>
+        <v>120237300</v>
       </c>
       <c r="B4" t="n">
         <v>78576</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447114</v>
+        <v>447112</v>
       </c>
       <c r="R4" t="n">
-        <v>6810324</v>
+        <v>6810364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237301</v>
+        <v>120237277</v>
       </c>
       <c r="B5" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447132</v>
+        <v>447039</v>
       </c>
       <c r="R5" t="n">
-        <v>6810359</v>
+        <v>6810326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237278</v>
+        <v>120237276</v>
       </c>
       <c r="B6" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447033</v>
+        <v>447061</v>
       </c>
       <c r="R6" t="n">
-        <v>6810319</v>
+        <v>6810331</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237293</v>
+        <v>120237292</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447133</v>
+        <v>447141</v>
       </c>
       <c r="R7" t="n">
-        <v>6810336</v>
+        <v>6810377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237292</v>
+        <v>120237302</v>
       </c>
       <c r="B8" t="n">
-        <v>78576</v>
+        <v>74654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447141</v>
+        <v>447132</v>
       </c>
       <c r="R8" t="n">
-        <v>6810377</v>
+        <v>6810361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237277</v>
+        <v>120237294</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447039</v>
+        <v>447133</v>
       </c>
       <c r="R9" t="n">
-        <v>6810326</v>
+        <v>6810330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120237302</v>
+        <v>120237289</v>
       </c>
       <c r="B10" t="n">
-        <v>74654</v>
+        <v>78576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447132</v>
+        <v>447108</v>
       </c>
       <c r="R10" t="n">
-        <v>6810361</v>
+        <v>6810318</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237291</v>
+        <v>120237298</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447116</v>
+        <v>447110</v>
       </c>
       <c r="R12" t="n">
-        <v>6810359</v>
+        <v>6810336</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237294</v>
+        <v>120237293</v>
       </c>
       <c r="B13" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2005,7 +2005,7 @@
         <v>447133</v>
       </c>
       <c r="R13" t="n">
-        <v>6810330</v>
+        <v>6810336</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120237298</v>
+        <v>120237278</v>
       </c>
       <c r="B14" t="n">
         <v>78576</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447110</v>
+        <v>447033</v>
       </c>
       <c r="R14" t="n">
-        <v>6810336</v>
+        <v>6810319</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120237300</v>
+        <v>120237297</v>
       </c>
       <c r="B15" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447112</v>
+        <v>447117</v>
       </c>
       <c r="R15" t="n">
-        <v>6810364</v>
+        <v>6810334</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237276</v>
+        <v>120237303</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447061</v>
+        <v>447119</v>
       </c>
       <c r="R16" t="n">
-        <v>6810331</v>
+        <v>6810321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237290</v>
+        <v>120237295</v>
       </c>
       <c r="B17" t="n">
         <v>78576</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447116</v>
+        <v>447114</v>
       </c>
       <c r="R17" t="n">
-        <v>6810359</v>
+        <v>6810324</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237289</v>
+        <v>120237291</v>
       </c>
       <c r="B18" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447108</v>
+        <v>447116</v>
       </c>
       <c r="R18" t="n">
-        <v>6810318</v>
+        <v>6810359</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237277</v>
+        <v>120237292</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447039</v>
+        <v>447141</v>
       </c>
       <c r="R5" t="n">
-        <v>6810326</v>
+        <v>6810377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237276</v>
+        <v>120237277</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447061</v>
+        <v>447039</v>
       </c>
       <c r="R6" t="n">
-        <v>6810331</v>
+        <v>6810326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237292</v>
+        <v>120237276</v>
       </c>
       <c r="B7" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447141</v>
+        <v>447061</v>
       </c>
       <c r="R7" t="n">
-        <v>6810377</v>
+        <v>6810331</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237301</v>
+        <v>120237299</v>
       </c>
       <c r="B2" t="n">
-        <v>77479</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447132</v>
+        <v>447102</v>
       </c>
       <c r="R2" t="n">
-        <v>6810359</v>
+        <v>6810347</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237290</v>
+        <v>120237277</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447116</v>
+        <v>447039</v>
       </c>
       <c r="R3" t="n">
-        <v>6810359</v>
+        <v>6810326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237300</v>
+        <v>120237295</v>
       </c>
       <c r="B4" t="n">
         <v>78576</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447112</v>
+        <v>447114</v>
       </c>
       <c r="R4" t="n">
-        <v>6810364</v>
+        <v>6810324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237292</v>
+        <v>120237301</v>
       </c>
       <c r="B5" t="n">
-        <v>78576</v>
+        <v>77479</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447141</v>
+        <v>447132</v>
       </c>
       <c r="R5" t="n">
-        <v>6810377</v>
+        <v>6810359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237277</v>
+        <v>120237303</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447039</v>
+        <v>447119</v>
       </c>
       <c r="R6" t="n">
-        <v>6810326</v>
+        <v>6810321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237276</v>
+        <v>120237298</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447061</v>
+        <v>447110</v>
       </c>
       <c r="R7" t="n">
-        <v>6810331</v>
+        <v>6810336</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237302</v>
+        <v>120237300</v>
       </c>
       <c r="B8" t="n">
-        <v>74654</v>
+        <v>78576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447132</v>
+        <v>447112</v>
       </c>
       <c r="R8" t="n">
-        <v>6810361</v>
+        <v>6810364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237294</v>
+        <v>120237278</v>
       </c>
       <c r="B9" t="n">
         <v>78576</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447133</v>
+        <v>447033</v>
       </c>
       <c r="R9" t="n">
-        <v>6810330</v>
+        <v>6810319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120237289</v>
+        <v>120237291</v>
       </c>
       <c r="B10" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447108</v>
+        <v>447116</v>
       </c>
       <c r="R10" t="n">
-        <v>6810318</v>
+        <v>6810359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120237299</v>
+        <v>120237294</v>
       </c>
       <c r="B11" t="n">
         <v>78576</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447102</v>
+        <v>447133</v>
       </c>
       <c r="R11" t="n">
-        <v>6810347</v>
+        <v>6810330</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237298</v>
+        <v>120237302</v>
       </c>
       <c r="B12" t="n">
-        <v>78576</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447110</v>
+        <v>447132</v>
       </c>
       <c r="R12" t="n">
-        <v>6810336</v>
+        <v>6810361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237293</v>
+        <v>120237292</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447133</v>
+        <v>447141</v>
       </c>
       <c r="R13" t="n">
-        <v>6810336</v>
+        <v>6810377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120237278</v>
+        <v>120237290</v>
       </c>
       <c r="B14" t="n">
         <v>78576</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447033</v>
+        <v>447116</v>
       </c>
       <c r="R14" t="n">
-        <v>6810319</v>
+        <v>6810359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237303</v>
+        <v>120237293</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447119</v>
+        <v>447133</v>
       </c>
       <c r="R16" t="n">
-        <v>6810321</v>
+        <v>6810336</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237295</v>
+        <v>120237289</v>
       </c>
       <c r="B17" t="n">
         <v>78576</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447114</v>
+        <v>447108</v>
       </c>
       <c r="R17" t="n">
-        <v>6810324</v>
+        <v>6810318</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237291</v>
+        <v>120237276</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447116</v>
+        <v>447061</v>
       </c>
       <c r="R18" t="n">
-        <v>6810359</v>
+        <v>6810331</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237299</v>
+        <v>120237292</v>
       </c>
       <c r="B2" t="n">
         <v>78576</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447102</v>
+        <v>447141</v>
       </c>
       <c r="R2" t="n">
-        <v>6810347</v>
+        <v>6810377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120237295</v>
+        <v>120237299</v>
       </c>
       <c r="B4" t="n">
         <v>78576</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447114</v>
+        <v>447102</v>
       </c>
       <c r="R4" t="n">
-        <v>6810324</v>
+        <v>6810347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120237301</v>
+        <v>120237297</v>
       </c>
       <c r="B5" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447132</v>
+        <v>447117</v>
       </c>
       <c r="R5" t="n">
-        <v>6810359</v>
+        <v>6810334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120237303</v>
+        <v>120237291</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447119</v>
+        <v>447116</v>
       </c>
       <c r="R6" t="n">
-        <v>6810321</v>
+        <v>6810359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120237298</v>
+        <v>120237300</v>
       </c>
       <c r="B7" t="n">
         <v>78576</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447110</v>
+        <v>447112</v>
       </c>
       <c r="R7" t="n">
-        <v>6810336</v>
+        <v>6810364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120237300</v>
+        <v>120237276</v>
       </c>
       <c r="B8" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447112</v>
+        <v>447061</v>
       </c>
       <c r="R8" t="n">
-        <v>6810364</v>
+        <v>6810331</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120237278</v>
+        <v>120237302</v>
       </c>
       <c r="B9" t="n">
-        <v>78576</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1510,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447033</v>
+        <v>447132</v>
       </c>
       <c r="R9" t="n">
-        <v>6810319</v>
+        <v>6810361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120237291</v>
+        <v>120237301</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447116</v>
+        <v>447132</v>
       </c>
       <c r="R10" t="n">
         <v>6810359</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120237294</v>
+        <v>120237293</v>
       </c>
       <c r="B11" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
         <v>447133</v>
       </c>
       <c r="R11" t="n">
-        <v>6810330</v>
+        <v>6810336</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120237302</v>
+        <v>120237303</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447132</v>
+        <v>447119</v>
       </c>
       <c r="R12" t="n">
-        <v>6810361</v>
+        <v>6810321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120237292</v>
+        <v>120237294</v>
       </c>
       <c r="B13" t="n">
         <v>78576</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447141</v>
+        <v>447133</v>
       </c>
       <c r="R13" t="n">
-        <v>6810377</v>
+        <v>6810330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120237297</v>
+        <v>120237295</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447117</v>
+        <v>447114</v>
       </c>
       <c r="R15" t="n">
-        <v>6810334</v>
+        <v>6810324</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120237293</v>
+        <v>120237289</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447133</v>
+        <v>447108</v>
       </c>
       <c r="R16" t="n">
-        <v>6810336</v>
+        <v>6810318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120237289</v>
+        <v>120237298</v>
       </c>
       <c r="B17" t="n">
         <v>78576</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447108</v>
+        <v>447110</v>
       </c>
       <c r="R17" t="n">
-        <v>6810318</v>
+        <v>6810336</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120237276</v>
+        <v>120237278</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,21 +2563,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447061</v>
+        <v>447033</v>
       </c>
       <c r="R18" t="n">
-        <v>6810331</v>
+        <v>6810319</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120237292</v>
+        <v>120237277</v>
       </c>
       <c r="B2" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447141</v>
+        <v>447039</v>
       </c>
       <c r="R2" t="n">
-        <v>6810377</v>
+        <v>6810326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120237277</v>
+        <v>120237292</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447039</v>
+        <v>447141</v>
       </c>
       <c r="R3" t="n">
-        <v>6810326</v>
+        <v>6810377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2662,6 +2662,238 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124851564</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Rotenstugan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>447118</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6810349</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Uno Skog, Klas Johansson, Hanna Mårshagen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124851561</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rotenstugan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>447141</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6810361</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Uno Skog, Klas Johansson, Hanna Mårshagen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -2664,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124851564</v>
+        <v>124851561</v>
       </c>
       <c r="B19" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447118</v>
+        <v>447141</v>
       </c>
       <c r="R19" t="n">
-        <v>6810349</v>
+        <v>6810361</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124851561</v>
+        <v>124851564</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447141</v>
+        <v>447118</v>
       </c>
       <c r="R20" t="n">
-        <v>6810361</v>
+        <v>6810349</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -2664,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124851561</v>
+        <v>124851564</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447141</v>
+        <v>447118</v>
       </c>
       <c r="R19" t="n">
-        <v>6810361</v>
+        <v>6810349</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124851564</v>
+        <v>124851561</v>
       </c>
       <c r="B20" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447118</v>
+        <v>447141</v>
       </c>
       <c r="R20" t="n">
-        <v>6810349</v>
+        <v>6810361</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -2667,7 +2667,7 @@
         <v>124851561</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>124851564</v>
       </c>
       <c r="B20" t="n">
-        <v>78842</v>
+        <v>78979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 59190-2023 artfynd.xlsx
+++ b/artfynd/A 59190-2023 artfynd.xlsx
@@ -2664,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124851561</v>
+        <v>124851564</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447141</v>
+        <v>447118</v>
       </c>
       <c r="R19" t="n">
-        <v>6810361</v>
+        <v>6810349</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,10 +2780,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124851564</v>
+        <v>124851561</v>
       </c>
       <c r="B20" t="n">
-        <v>78979</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447118</v>
+        <v>447141</v>
       </c>
       <c r="R20" t="n">
-        <v>6810349</v>
+        <v>6810361</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
